--- a/artfynd/A 55586-2020 artfynd.xlsx
+++ b/artfynd/A 55586-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55586-2020 artfynd.xlsx
+++ b/artfynd/A 55586-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2116,6 +2116,108 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128340317</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97356</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Holmfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>748537</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7252284</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55586-2020 artfynd.xlsx
+++ b/artfynd/A 55586-2020 artfynd.xlsx
@@ -2121,7 +2121,7 @@
         <v>128340317</v>
       </c>
       <c r="B15" t="n">
-        <v>97356</v>
+        <v>97361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 55586-2020 artfynd.xlsx
+++ b/artfynd/A 55586-2020 artfynd.xlsx
@@ -2121,7 +2121,7 @@
         <v>128340317</v>
       </c>
       <c r="B15" t="n">
-        <v>97361</v>
+        <v>97454</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 55586-2020 artfynd.xlsx
+++ b/artfynd/A 55586-2020 artfynd.xlsx
@@ -2121,7 +2121,7 @@
         <v>128340317</v>
       </c>
       <c r="B15" t="n">
-        <v>97454</v>
+        <v>97466</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 55586-2020 artfynd.xlsx
+++ b/artfynd/A 55586-2020 artfynd.xlsx
@@ -2121,7 +2121,7 @@
         <v>128340317</v>
       </c>
       <c r="B15" t="n">
-        <v>97466</v>
+        <v>97468</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 55586-2020 artfynd.xlsx
+++ b/artfynd/A 55586-2020 artfynd.xlsx
@@ -2121,7 +2121,7 @@
         <v>128340317</v>
       </c>
       <c r="B15" t="n">
-        <v>97468</v>
+        <v>97469</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 55586-2020 artfynd.xlsx
+++ b/artfynd/A 55586-2020 artfynd.xlsx
@@ -2121,7 +2121,7 @@
         <v>128340317</v>
       </c>
       <c r="B15" t="n">
-        <v>97469</v>
+        <v>97496</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 55586-2020 artfynd.xlsx
+++ b/artfynd/A 55586-2020 artfynd.xlsx
@@ -2121,7 +2121,7 @@
         <v>128340317</v>
       </c>
       <c r="B15" t="n">
-        <v>97496</v>
+        <v>97509</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 55586-2020 artfynd.xlsx
+++ b/artfynd/A 55586-2020 artfynd.xlsx
@@ -2121,7 +2121,7 @@
         <v>128340317</v>
       </c>
       <c r="B15" t="n">
-        <v>97509</v>
+        <v>97513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
